--- a/local/templates/competitionResults/FlatResults.xlsx
+++ b/local/templates/competitionResults/FlatResults.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Library/Application Support/owlcms/65.0.1/local/templates/competitionResults/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/templates/competitionResults/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C02BCBB-3E4A-DC47-9525-49B18EE42D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D764872-69AB-3040-BCF3-C4C2B37AE842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14040" yWindow="3820" windowWidth="45920" windowHeight="18400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:area(lastCell="T2")</t>
+          <t>jx:area(lastCell="U2")</t>
         </r>
       </text>
     </comment>
@@ -89,7 +89,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">  lastCell="T2"
+          <t xml:space="preserve">  lastCell="U2"
 </t>
         </r>
         <r>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="119">
   <si>
     <t>Men's 16-17 Age Group</t>
   </si>
@@ -459,6 +459,12 @@
   </si>
   <si>
     <t>${athlete.category.ageGroup.computedScoringSystem == 'TOTAL' ? "" : !athlete.categoryFinished ? "-" : athlete.individualEligibilityStatus.isDisqualification() ? "DSQ" : athlete.categoryScoreRank == 0 ? "DNF" : athlete.categoryScoreRank == -1 ? "ext" : athlete.categoryScoreRank}</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>${athlete.club}</t>
   </si>
 </sst>
 </file>
@@ -951,22 +957,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="2" customWidth="1"/>
-    <col min="10" max="15" width="11.6640625" customWidth="1"/>
-    <col min="16" max="16" width="11.33203125" customWidth="1"/>
+    <col min="3" max="5" width="19" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.5" style="2" customWidth="1"/>
+    <col min="11" max="16" width="11.6640625" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="23" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>107</v>
       </c>
@@ -979,56 +985,59 @@
       <c r="D1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>108</v>
       </c>
@@ -1041,73 +1050,76 @@
       <c r="D2" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="J2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="R2" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="S2" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="T2" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="U2" s="16"/>
       <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <dataValidations count="4">
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" sqref="E3:G1002" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="date" allowBlank="1" showErrorMessage="1" sqref="F3:H1002" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>36526</formula1>
       <formula2>54789</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showErrorMessage="1" sqref="A3:A1002 C3:D1002 B4:B1002" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showErrorMessage="1" sqref="A3:A1002 C3:E1002 B4:B1002" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="I3:I1002" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="J3:J1002" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>20</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" sqref="J3:O1002" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" sqref="K3:P1002" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>-500</formula1>
       <formula2>500</formula2>
     </dataValidation>
